--- a/xlsx/Power/pgroups2.xlsx
+++ b/xlsx/Power/pgroups2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C674B2-E3D0-4189-A1C3-E31B30F1A10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFE1B0A-ECF7-4D4D-BF52-B5871F722DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{509F990C-B9A6-4AB9-9148-7BB2FB1DCE09}"/>
+    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{509F990C-B9A6-4AB9-9148-7BB2FB1DCE09}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="C1">
-        <v>8.6999999999999994E-2</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="D1">
-        <v>0.24399999999999999</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="E1">
-        <v>0.437</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="F1">
-        <v>0.57299999999999995</v>
+        <v>0.751</v>
       </c>
       <c r="G1">
-        <v>0.70299999999999996</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="H1">
-        <v>0.78500000000000003</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="I1">
-        <v>0.85</v>
+        <v>0.92100000000000004</v>
       </c>
       <c r="J1">
-        <v>0.88100000000000001</v>
+        <v>0.92400000000000004</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="C2">
-        <v>9.5000000000000001E-2</v>
+        <v>0.437</v>
       </c>
       <c r="D2">
-        <v>0.248</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="E2">
-        <v>0.437</v>
+        <v>0.65400000000000003</v>
       </c>
       <c r="F2">
-        <v>0.56699999999999995</v>
+        <v>0.745</v>
       </c>
       <c r="G2">
-        <v>0.69399999999999995</v>
+        <v>0.82599999999999996</v>
       </c>
       <c r="H2">
-        <v>0.77500000000000002</v>
+        <v>0.877</v>
       </c>
       <c r="I2">
-        <v>0.83299999999999996</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="J2">
-        <v>0.86499999999999999</v>
+        <v>0.91400000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.27100000000000002</v>
       </c>
       <c r="C3">
-        <v>0.433</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="D3">
-        <v>0.49199999999999999</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E3">
-        <v>0.61</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="F3">
-        <v>0.68200000000000005</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="G3">
         <v>0.755</v>
       </c>
       <c r="H3">
-        <v>0.80500000000000005</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="I3">
-        <v>0.85599999999999998</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="J3">
-        <v>0.86699999999999999</v>
+        <v>0.86599999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.14099999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="B4">
-        <v>0.25600000000000001</v>
+        <v>0.246</v>
       </c>
       <c r="C4">
-        <v>0.36199999999999999</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="D4">
-        <v>0.44400000000000001</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="E4">
         <v>0.54200000000000004</v>
       </c>
       <c r="F4">
-        <v>0.61299999999999999</v>
+        <v>0.61099999999999999</v>
       </c>
       <c r="G4">
         <v>0.68799999999999994</v>
       </c>
       <c r="H4">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="I4">
-        <v>0.78600000000000003</v>
+        <v>0.78700000000000003</v>
       </c>
       <c r="J4">
-        <v>0.82499999999999996</v>
+        <v>0.82099999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="C5">
-        <v>9.6000000000000002E-2</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="D5">
-        <v>0.40200000000000002</v>
+        <v>0.83399999999999996</v>
       </c>
       <c r="E5">
-        <v>0.69</v>
+        <v>0.89800000000000002</v>
       </c>
       <c r="F5">
-        <v>0.83399999999999996</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="G5">
-        <v>0.85699999999999998</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="H5">
-        <v>0.90300000000000002</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="I5">
-        <v>0.93100000000000005</v>
+        <v>0.96899999999999997</v>
       </c>
       <c r="J5">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.29699999999999999</v>
       </c>
       <c r="C6">
-        <v>0.57399999999999995</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="D6">
-        <v>0.56499999999999995</v>
+        <v>0.505</v>
       </c>
       <c r="E6">
-        <v>0.64900000000000002</v>
+        <v>0.60499999999999998</v>
       </c>
       <c r="F6">
-        <v>0.72099999999999997</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="G6">
-        <v>0.80800000000000005</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="H6">
-        <v>0.84499999999999997</v>
+        <v>0.83199999999999996</v>
       </c>
       <c r="I6">
-        <v>0.88400000000000001</v>
+        <v>0.877</v>
       </c>
       <c r="J6">
-        <v>0.89500000000000002</v>
+        <v>0.88300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,25 +596,25 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="C7">
-        <v>0.38500000000000001</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="D7">
         <v>0.48299999999999998</v>
       </c>
       <c r="E7">
-        <v>0.57799999999999996</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="F7">
-        <v>0.65800000000000003</v>
+        <v>0.66</v>
       </c>
       <c r="G7">
-        <v>0.75600000000000001</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="H7">
         <v>0.80100000000000005</v>
       </c>
       <c r="I7">
-        <v>0.84699999999999998</v>
+        <v>0.84799999999999998</v>
       </c>
       <c r="J7">
         <v>0.86599999999999999</v>
@@ -628,28 +628,28 @@
         <v>0.17799999999999999</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="D8">
-        <v>5.8999999999999997E-2</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="E8">
-        <v>0.157</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="F8">
-        <v>0.247</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="G8">
-        <v>0.36099999999999999</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="H8">
-        <v>0.41</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I8">
-        <v>0.23499999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J8">
-        <v>0.26300000000000001</v>
+        <v>0.70099999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.17899999999999999</v>
       </c>
       <c r="C9">
-        <v>0.41399999999999998</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="D9">
-        <v>0.88900000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="E9">
-        <v>0.72599999999999998</v>
+        <v>0.23</v>
       </c>
       <c r="F9">
-        <v>0.39</v>
+        <v>0.224</v>
       </c>
       <c r="G9">
-        <v>0.36899999999999999</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="H9">
-        <v>0.379</v>
+        <v>0.33</v>
       </c>
       <c r="I9">
-        <v>0.39300000000000002</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="J9">
-        <v>0.439</v>
+        <v>0.42699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/pgroups2.xlsx
+++ b/xlsx/Power/pgroups2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFE1B0A-ECF7-4D4D-BF52-B5871F722DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3670E4-478F-4D63-9873-2D9797503115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{509F990C-B9A6-4AB9-9148-7BB2FB1DCE09}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{509F990C-B9A6-4AB9-9148-7BB2FB1DCE09}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,7 +398,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.13800000000000001</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="B1">
         <v>0.30599999999999999</v>
@@ -407,13 +407,13 @@
         <v>0.45200000000000001</v>
       </c>
       <c r="D1">
-        <v>0.57299999999999995</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="E1">
-        <v>0.68200000000000005</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="F1">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="G1">
         <v>0.84099999999999997</v>
@@ -422,59 +422,59 @@
         <v>0.88400000000000001</v>
       </c>
       <c r="I1">
-        <v>0.92100000000000004</v>
+        <v>0.92300000000000004</v>
       </c>
       <c r="J1">
-        <v>0.92400000000000004</v>
+        <v>0.92600000000000005</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.13500000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="B2">
-        <v>0.30399999999999999</v>
+        <v>0.308</v>
       </c>
       <c r="C2">
         <v>0.437</v>
       </c>
       <c r="D2">
-        <v>0.54300000000000004</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="E2">
-        <v>0.65400000000000003</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="F2">
         <v>0.745</v>
       </c>
       <c r="G2">
-        <v>0.82599999999999996</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="H2">
-        <v>0.877</v>
+        <v>0.871</v>
       </c>
       <c r="I2">
-        <v>0.90200000000000002</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="J2">
-        <v>0.91400000000000003</v>
+        <v>0.91600000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.13100000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="B3">
-        <v>0.27100000000000002</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="C3">
-        <v>0.38800000000000001</v>
+        <v>0.39200000000000002</v>
       </c>
       <c r="D3">
-        <v>0.48199999999999998</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="E3">
-        <v>0.60599999999999998</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="F3">
         <v>0.67700000000000005</v>
@@ -483,13 +483,13 @@
         <v>0.755</v>
       </c>
       <c r="H3">
-        <v>0.80200000000000005</v>
+        <v>0.80700000000000005</v>
       </c>
       <c r="I3">
-        <v>0.85499999999999998</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="J3">
-        <v>0.86599999999999999</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -497,118 +497,118 @@
         <v>0.126</v>
       </c>
       <c r="B4">
-        <v>0.246</v>
+        <v>0.249</v>
       </c>
       <c r="C4">
-        <v>0.35599999999999998</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="D4">
         <v>0.44600000000000001</v>
       </c>
       <c r="E4">
-        <v>0.54200000000000004</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="F4">
-        <v>0.61099999999999999</v>
+        <v>0.61299999999999999</v>
       </c>
       <c r="G4">
-        <v>0.68799999999999994</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="H4">
         <v>0.749</v>
       </c>
       <c r="I4">
-        <v>0.78700000000000003</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="J4">
-        <v>0.82099999999999995</v>
+        <v>0.82799999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.245</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.53700000000000003</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>0.72499999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="D5">
-        <v>0.83399999999999996</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>0.89800000000000002</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F5">
-        <v>0.91800000000000004</v>
+        <v>3.1E-2</v>
       </c>
       <c r="G5">
-        <v>0.93500000000000005</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="H5">
-        <v>0.95299999999999996</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="I5">
-        <v>0.96899999999999997</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="J5">
-        <v>0.98</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.13100000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="B6">
-        <v>0.29699999999999999</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="C6">
-        <v>0.41699999999999998</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="D6">
-        <v>0.505</v>
+        <v>0.502</v>
       </c>
       <c r="E6">
-        <v>0.60499999999999998</v>
+        <v>0.60099999999999998</v>
       </c>
       <c r="F6">
-        <v>0.70199999999999996</v>
+        <v>0.69899999999999995</v>
       </c>
       <c r="G6">
-        <v>0.79900000000000004</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="H6">
-        <v>0.83199999999999996</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="I6">
-        <v>0.877</v>
+        <v>0.874</v>
       </c>
       <c r="J6">
-        <v>0.88300000000000001</v>
+        <v>0.88800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.13100000000000001</v>
+        <v>0.129</v>
       </c>
       <c r="B7">
-        <v>0.28499999999999998</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="C7">
-        <v>0.39200000000000002</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="D7">
-        <v>0.48299999999999998</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E7">
         <v>0.57199999999999995</v>
       </c>
       <c r="F7">
-        <v>0.66</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="G7">
-        <v>0.76100000000000001</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="H7">
         <v>0.80100000000000005</v>
@@ -634,10 +634,10 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="E8">
-        <v>0.43099999999999999</v>
+        <v>0.438</v>
       </c>
       <c r="F8">
-        <v>0.47099999999999997</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="G8">
         <v>0.52400000000000002</v>
@@ -646,7 +646,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I8">
-        <v>0.7</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="J8">
         <v>0.70099999999999996</v>
@@ -657,31 +657,31 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="B9">
-        <v>0.17899999999999999</v>
+        <v>0.18</v>
       </c>
       <c r="C9">
-        <v>0.13800000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D9">
         <v>0.14199999999999999</v>
       </c>
       <c r="E9">
-        <v>0.23</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="F9">
-        <v>0.224</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="G9">
-        <v>0.30399999999999999</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="H9">
-        <v>0.33</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="I9">
         <v>0.36499999999999999</v>
       </c>
       <c r="J9">
-        <v>0.42699999999999999</v>
+        <v>0.43099999999999999</v>
       </c>
     </row>
   </sheetData>
